--- a/03_Continuous/03_Profile_Clusters/c_data/profile_clusters.xlsx
+++ b/03_Continuous/03_Profile_Clusters/c_data/profile_clusters.xlsx
@@ -13469,7 +13469,7 @@
     <t>corrected</t>
   </si>
   <si>
-    <t>01_Processing/03_Blood_Correction/c_data/proteins_corrected.rds</t>
+    <t>01_Processing/03_Blood_Correction/c_data/blood_correction.rds</t>
   </si>
   <si>
     <t>35fac30909b3ec9c4ae9469c4edc26a0</t>
@@ -13478,7 +13478,7 @@
     <t>associations</t>
   </si>
   <si>
-    <t>03_Continuous/01_Trait_Associations/c_data/associations.rds</t>
+    <t>03_Continuous/01_Trait_Associations/c_data/trait_associations.rds</t>
   </si>
   <si>
     <t>bcc122524b1e4253791773a6fe889a66</t>
@@ -13496,7 +13496,7 @@
     <t>modules</t>
   </si>
   <si>
-    <t>01_Processing/06_Module_Building/c_data/modules.rds</t>
+    <t>01_Processing/06_Module_Building/c_data/module_building.rds</t>
   </si>
   <si>
     <t>32c36eae09056636394bdb0714dd608a</t>
